--- a/reports/Leetcode Daily Report 3 year_2026-10-22.xlsx
+++ b/reports/Leetcode Daily Report 3 year_2026-10-22.xlsx
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
